--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.50.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.50.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -823,7 +823,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.50.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.50.xlsx
@@ -422,16 +422,16 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="51" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -595,18 +595,18 @@
       <c r="G2" s="1" t="inlineStr"/>
       <c r="H2" s="1" t="inlineStr"/>
       <c r="I2" s="1" t="inlineStr"/>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>L128: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: subpo Ã¦ ena for the same, or the Master</t>
-        </is>
-      </c>
+      <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L18: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜s former</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]43</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]43</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L4: isolated marker/symbol line :: 0</t>
@@ -614,7 +614,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L21: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]43</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -645,7 +645,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>87</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -657,7 +657,7 @@
       <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L21: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L21: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L107: isolated marker/symbol line :: *</t>
+          <t>L21: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -706,11 +706,7 @@
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr"/>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L88: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: wo clearâ€˜</t>
-        </is>
-      </c>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
@@ -718,7 +714,11 @@
           <t>L32: symbol-only separator/garbage line :: 183.</t>
         </is>
       </c>
-      <c r="O4" s="1" t="inlineStr"/>
+      <c r="O4" s="1" t="inlineStr">
+        <is>
+          <t>L97: isolated marker/symbol line :: s:—</t>
+        </is>
+      </c>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr"/>
       <c r="R4" s="1" t="inlineStr"/>
@@ -738,12 +738,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -753,11 +753,7 @@
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr"/>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L97: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: s:â€”</t>
-        </is>
-      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -765,7 +761,11 @@
           <t>L37: isolated marker/symbol line :: 43</t>
         </is>
       </c>
-      <c r="O5" s="1" t="inlineStr"/>
+      <c r="O5" s="1" t="inlineStr">
+        <is>
+          <t>L107: isolated marker/symbol line :: *</t>
+        </is>
+      </c>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr"/>
       <c r="R5" s="1" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
